--- a/dashboard-its-chile/ITS_Chile_BaseDatos.xlsx
+++ b/dashboard-its-chile/ITS_Chile_BaseDatos.xlsx
@@ -22,7 +22,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MundoLargo" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CascadaLargo" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuiaLarga" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPILargo" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SimColegios" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SimAcceso" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SimEfecto" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SimCondon" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SimIndicadores" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SimSupuestos" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -75,11 +83,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -235,12 +246,67 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="Fuentes" displayName="Fuentes" ref="A1:C35" headerRowCount="1">
-  <autoFilter ref="A1:C35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="KPI" displayName="KPI" ref="A1:I11" headerRowCount="1">
+  <autoFilter ref="A1:I11"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="Orden"/>
+    <tableColumn id="2" name="Area"/>
+    <tableColumn id="3" name="KPI"/>
+    <tableColumn id="4" name="Valor"/>
+    <tableColumn id="5" name="Formula"/>
+    <tableColumn id="6" name="QueMide"/>
+    <tableColumn id="7" name="PorQue"/>
+    <tableColumn id="8" name="Meta"/>
+    <tableColumn id="9" name="FuenteID"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="KPILargo" displayName="KPILargo" ref="A1:E71" headerRowCount="1">
+  <autoFilter ref="A1:E71"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="OrdenKPI"/>
+    <tableColumn id="2" name="KPI"/>
+    <tableColumn id="3" name="OrdenCampo"/>
+    <tableColumn id="4" name="Campo"/>
+    <tableColumn id="5" name="Valor"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="SimColegios" displayName="SimColegios" ref="A1:B12" headerRowCount="1">
+  <autoFilter ref="A1:B12"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="Porcentaje"/>
+    <tableColumn id="2" name="Orden"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="SimAcceso" displayName="SimAcceso" ref="A1:C3" headerRowCount="1">
+  <autoFilter ref="A1:C3"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="FuenteID"/>
-    <tableColumn id="2" name="Referencia"/>
-    <tableColumn id="3" name="URL"/>
+    <tableColumn id="1" name="Opcion"/>
+    <tableColumn id="2" name="Valor"/>
+    <tableColumn id="3" name="Orden"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="SimEfecto" displayName="SimEfecto" ref="A1:C3" headerRowCount="1">
+  <autoFilter ref="A1:C3"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Escenario"/>
+    <tableColumn id="2" name="Porcentaje"/>
+    <tableColumn id="3" name="Orden"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
@@ -257,6 +323,56 @@
     <tableColumn id="5" name="TasaPor100mil"/>
     <tableColumn id="6" name="Nota"/>
     <tableColumn id="7" name="FuenteID"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="SimCondon" displayName="SimCondon" ref="A1:B6" headerRowCount="1">
+  <autoFilter ref="A1:B6"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="Puntos"/>
+    <tableColumn id="2" name="Orden"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="SimIndicadores" displayName="SimIndicadores" ref="A1:D4" headerRowCount="1">
+  <autoFilter ref="A1:D4"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Orden"/>
+    <tableColumn id="2" name="Indicador"/>
+    <tableColumn id="3" name="Base"/>
+    <tableColumn id="4" name="Tipo"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="SimSupuestos" displayName="SimSupuestos" ref="A1:E8" headerRowCount="1">
+  <autoFilter ref="A1:E8"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Orden"/>
+    <tableColumn id="2" name="Supuesto"/>
+    <tableColumn id="3" name="Valor"/>
+    <tableColumn id="4" name="PorQue"/>
+    <tableColumn id="5" name="FuenteID"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="Fuentes" displayName="Fuentes" ref="A1:C40" headerRowCount="1">
+  <autoFilter ref="A1:C35"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="FuenteID"/>
+    <tableColumn id="2" name="Referencia"/>
+    <tableColumn id="3" name="URL"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
@@ -669,9 +785,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -3973,607 +4087,2362 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
+          <t>Orden</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>QueMide</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>PorQue</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>FuenteID</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Tendencias</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia notificada de sífilis</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>55,2 por 100 mil (2025)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos notificados en el año ÷ población × 100.000</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Cuántas personas se diagnostican con sífilis cada año, ajustado por tamaño de la población</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Permite comparar años, regiones y países y ver si la transmisión sube o baja; es enfermedad de notificación obligatoria</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Bajar la tendencia; Unión Europea: 10,8</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>S2;S16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Tendencias</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia notificada de gonorrea</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>13,3 por 100 mil (2025)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos notificados en el año ÷ población × 100.000</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Magnitud y tendencia de la gonorrea</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Su aumento alerta sobre relaciones sin condón y riesgo de resistencia a antibióticos</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Bajar la tendencia; Unión Europea: 26,9</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>S4;S17</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Tendencias</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Nuevos diagnósticos de VIH confirmados</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>4.313 casos (2025)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Número de casos confirmados por el ISP en el año</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Cuántas personas se diagnostican con VIH cada año</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Mide la llegada al diagnóstico; más testeo puede subir el número aunque baje la transmisión</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Reducir nuevas infecciones (ONUSIDA)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Tendencias</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de sífilis congénita</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>0,41 por 1.000 nacidos vivos</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Casos de sífilis congénita ÷ nacidos vivos × 1.000</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Cuántas guaguas nacen con sífilis transmitida durante el embarazo</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Es evitable con VDRL en el control prenatal y tratamiento oportuno de la gestante y su pareja</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Eliminación OPS: ≤ 0,5 por 1.000 nacidos vivos</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>S19;S29</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>¿A quiénes afecta?</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Tasa específica por edad</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sífilis 20 a 29: 111,3 por 100 mil</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Casos del grupo de edad ÷ población de ese grupo × 100.000</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>En qué edades se concentra cada ITS</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Orienta dónde focalizar educación, testeo y anticoncepción con condón</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>¿A quiénes afecta?</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Razón de tasas hombre:mujer</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>VIH 4,7 : 1 (2023)</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Tasa en hombres ÷ tasa en mujeres</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Cuántas veces más afecta a hombres que a mujeres</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Muestra brechas por sexo y dónde crece más rápido (gonorrea en mujeres × 3,8)</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>S3;S11</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Chile y el mundo</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: diagnóstico</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>95% conoce su diagnóstico</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Personas diagnosticadas ÷ personas que viven con VIH × 100</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Qué parte de las personas con VIH sabe que lo tiene</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Sin diagnóstico no hay tratamiento ni prevención de nuevos contagios</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>95% (ONUSIDA 2030)</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>S13;S14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Chile y el mundo</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: tratamiento</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>71% en tratamiento</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Personas en tratamiento antirretroviral ÷ personas que viven con VIH × 100</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Qué parte de las personas con VIH recibe tratamiento</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Es el punto débil de Chile: 21.915 personas diagnosticadas no están en tratamiento</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>95% (ONUSIDA 2030)</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Chile y el mundo</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: carga viral suprimida</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>68% con carga viral suprimida</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Personas con carga viral indetectable ÷ personas que viven con VIH × 100</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Qué parte logra que el virus no se detecte en sangre</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Indetectable = intransmisible: es el KPI que mejor refleja el control de la epidemia</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>95% (ONUSIDA 2030)</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Chile y el mundo</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de transmisión vertical de VIH</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Recién nacidos con VIH ÷ recién nacidos de madres con VIH × 100</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Cuántas guaguas adquieren el VIH de su madre</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Mide la calidad del protocolo de prevención en el embarazo, el parto y la lactancia</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>&lt; 2% (meta OPS de eliminación)</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>S19</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>OrdenKPI</t>
+        </is>
+      </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Referencia</t>
+          <t>KPI</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>OrdenCampo</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Campo</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Rev Chil Infectol 2025. Caracterización epidemiológica de la sífilis en Chile 2018–2022 (datos de notificación MINSAL).</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://revinf.cl/index.php/revinf/article/download/2492/1138</t>
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia notificada de sífilis</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>55,2 por 100 mil (2025)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MINSAL, Informe Epidemiológico Anual 2025 de sífilis (vía Meganoticias, 19-08-2026).</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.meganoticias.cl/nacional/529712-sifilis-alcanza-record-historico-en-chile-casos-se-disparan-aumento-entre-adultos-mayores-y-mujeres-60-anos-19-08-2026.html</t>
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia notificada de sífilis</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos notificados en el año ÷ población × 100.000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia notificada de sífilis</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Cuántas personas se diagnostican con sífilis cada año, ajustado por tamaño de la población</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia notificada de sífilis</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Permite comparar años, regiones y países y ver si la transmisión sube o baja; es enfermedad de notificación obligatoria</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia notificada de sífilis</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Bajar la tendencia; Unión Europea: 10,8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia notificada de sífilis</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Tendencias</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia notificada de sífilis</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>S2;S16</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia notificada de gonorrea</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>13,3 por 100 mil (2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia notificada de gonorrea</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos notificados en el año ÷ población × 100.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia notificada de gonorrea</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Magnitud y tendencia de la gonorrea</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia notificada de gonorrea</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Su aumento alerta sobre relaciones sin condón y riesgo de resistencia a antibióticos</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia notificada de gonorrea</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Bajar la tendencia; Unión Europea: 26,9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia notificada de gonorrea</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Tendencias</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia notificada de gonorrea</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>S4;S17</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Nuevos diagnósticos de VIH confirmados</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>4.313 casos (2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Nuevos diagnósticos de VIH confirmados</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Número de casos confirmados por el ISP en el año</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Nuevos diagnósticos de VIH confirmados</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Cuántas personas se diagnostican con VIH cada año</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Nuevos diagnósticos de VIH confirmados</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Mide la llegada al diagnóstico; más testeo puede subir el número aunque baje la transmisión</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Nuevos diagnósticos de VIH confirmados</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Reducir nuevas infecciones (ONUSIDA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Nuevos diagnósticos de VIH confirmados</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Tendencias</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Nuevos diagnósticos de VIH confirmados</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de sífilis congénita</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>0,41 por 1.000 nacidos vivos</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de sífilis congénita</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Casos de sífilis congénita ÷ nacidos vivos × 1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de sífilis congénita</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Cuántas guaguas nacen con sífilis transmitida durante el embarazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de sífilis congénita</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Es evitable con VDRL en el control prenatal y tratamiento oportuno de la gestante y su pareja</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de sífilis congénita</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Eliminación OPS: ≤ 0,5 por 1.000 nacidos vivos</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de sífilis congénita</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Tendencias</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de sífilis congénita</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>S19;S29</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Tasa específica por edad</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Sífilis 20 a 29: 111,3 por 100 mil</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Tasa específica por edad</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Casos del grupo de edad ÷ población de ese grupo × 100.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Tasa específica por edad</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>En qué edades se concentra cada ITS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Tasa específica por edad</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Orienta dónde focalizar educación, testeo y anticoncepción con condón</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Tasa específica por edad</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Tasa específica por edad</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>¿A quiénes afecta?</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Tasa específica por edad</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>MINSAL, reporte 2025 de sífilis y gonorrea (vía Emol, 12-07-2026).</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.emol.com/noticias/Nacional/2026/07/12/1205310/sifilis-gonorrea-chile-reporte-minsal.html</t>
-        </is>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Razón de tasas hombre:mujer</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>VIH 4,7 : 1 (2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Razón de tasas hombre:mujer</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Tasa en hombres ÷ tasa en mujeres</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Razón de tasas hombre:mujer</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Cuántas veces más afecta a hombres que a mujeres</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Razón de tasas hombre:mujer</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Muestra brechas por sexo y dónde crece más rápido (gonorrea en mujeres × 3,8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Razón de tasas hombre:mujer</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Razón de tasas hombre:mujer</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>¿A quiénes afecta?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Razón de tasas hombre:mujer</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>S3;S11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: diagnóstico</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>95% conoce su diagnóstico</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: diagnóstico</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Personas diagnosticadas ÷ personas que viven con VIH × 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: diagnóstico</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Qué parte de las personas con VIH sabe que lo tiene</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: diagnóstico</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Sin diagnóstico no hay tratamiento ni prevención de nuevos contagios</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: diagnóstico</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>95% (ONUSIDA 2030)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: diagnóstico</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Chile y el mundo</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: diagnóstico</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>S13;S14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: tratamiento</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>71% en tratamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: tratamiento</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Personas en tratamiento antirretroviral ÷ personas que viven con VIH × 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: tratamiento</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Qué parte de las personas con VIH recibe tratamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: tratamiento</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Es el punto débil de Chile: 21.915 personas diagnosticadas no están en tratamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: tratamiento</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>95% (ONUSIDA 2030)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: tratamiento</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Chile y el mundo</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: tratamiento</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: carga viral suprimida</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>68% con carga viral suprimida</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: carga viral suprimida</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Personas con carga viral indetectable ÷ personas que viven con VIH × 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: carga viral suprimida</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Qué parte logra que el virus no se detecte en sangre</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: carga viral suprimida</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Indetectable = intransmisible: es el KPI que mejor refleja el control de la epidemia</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: carga viral suprimida</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>95% (ONUSIDA 2030)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: carga viral suprimida</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Chile y el mundo</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Cascada VIH 95-95-95: carga viral suprimida</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de transmisión vertical de VIH</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de transmisión vertical de VIH</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Recién nacidos con VIH ÷ recién nacidos de madres con VIH × 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de transmisión vertical de VIH</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Cuántas guaguas adquieren el VIH de su madre</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de transmisión vertical de VIH</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Mide la calidad del protocolo de prevención en el embarazo, el parto y la lactancia</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de transmisión vertical de VIH</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>&lt; 2% (meta OPS de eliminación)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de transmisión vertical de VIH</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Chile y el mundo</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de transmisión vertical de VIH</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>S19</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Porcentaje</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Orden</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MINSAL, gonorrea y sífilis en jóvenes 2025 (vía BioBioChile, 06-07-2026).</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.biobiochile.cl/noticias/salud-y-bienestar/cuerpo/2026/07/06/registro-mas-alto-de-la-decada-aumentan-los-contagios-de-gonorrea-y-sifilis-entre-jovenes-chilenos.shtml</t>
-        </is>
+      <c r="A5" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>MINSAL, sífilis en personas de 60 años o más (vía BioBioChile, 19-08-2026).</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.biobiochile.cl/noticias/nacional/chile/2026/08/19/sifilis-alcanza-record-en-chile-tasa-entre-mujeres-mayores-de-60-anos-se-duplico-en-cuatro-anos.shtml</t>
-        </is>
+      <c r="A6" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>MINSAL, ITS en menores de 15 años (vía T13, 19-08-2026).</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.t13.cl/noticia/nacional/aumento-ets-chile-destaca-incremento-gonorrea-menores-15-anos-sifilis-record-19-8-2026</t>
-        </is>
+      <c r="A7" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ISP, confirmación de VIH 2010–2019 (documento Cámara de Diputados).</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.camara.cl/verDoc.aspx?prmID=172229&amp;prmTIPO=DOCUMENTOCOMISION</t>
-        </is>
+      <c r="A8" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ISP, VIH 2022 (vía BioBioChile, 31-07-2023).</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.biobiochile.cl/noticias/nacional/chile/2023/07/31/isp-casos-de-vih-aumenta-7-en-un-ano-y-mayor-tasa-de-diagnostico-esta-asociada-a-hombres.shtml</t>
-        </is>
+      <c r="A9" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ISP, VIH 2024 (vía El Ciudadano).</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.elciudadano.com/?p=1117920</t>
-        </is>
+      <c r="A10" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ISP, VIH 2025 (vía El Desconcierto, 23-03-2026).</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://eldesconcierto.cl/2026/03/23/vih-una-inercia-preocupante</t>
-        </is>
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>S11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>VIH 2023 por sexo y edad (vía El Mostrador, 01-12-2025).</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://www.elmostrador.cl/agenda-pais/vida-en-linea/2025/12/01/vih-en-chile-expertos-alertan-fuerte-aumento-de-casos-en-jovenes-y-baja-percepcion-de-riesgo/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ONUSIDA, personas que viven con VIH en Chile (vía The Clinic, 25-06-2026).</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://www.theclinic.cl/2026/06/25/chile-registra-un-aumento-de-casos-de-vih-de-un-86-en-los-ultimos-10-anos-onu-alerta-sobre-riesgos-de-no-avanzar-en-prevencion-de-contagios/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>S13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Cascada VIH Chile: diagnosticados sin tratamiento (vía BioBioChile, 03-09-2026).</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://www.biobiochile.cl/noticias/nacional/chile/2026/09/03/alerta-por-vih-en-chile-mas-de-21-mil-diagnosticados-no-reciben-tratamiento.shtml</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>S14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ONUSIDA, informe Latinoamérica 2025.</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://unaids.org.br/wp-content/uploads/2025/07/25-07-09-BLS25218-GR-RP-LATAM-PTBR-2.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>S15</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ONUSIDA, ficha mundial.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://www.unaids.org/en/resources/fact-sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>S16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ECDC, sífilis, informe anual 2024.</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://www.ecdc.europa.eu/en/publications-data/syphilis-annual-epidemiological-report-2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>S17</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ECDC, gonorrea, informe anual 2024.</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://www.ecdc.europa.eu/en/publications-data/gonorrhoea-annual-epidemiological-report-2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>S18</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ECDC, vigilancia de VIH/sida en Europa 2025 (datos 2024).</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://www.ecdc.europa.eu/en/publications-data/hivaids-surveillance-europe-2025-2024-data</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>S19</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>OPS, perfil de país Chile.</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://hia.paho.org/en/country-profiles/chile</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>S20</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>OPS, aumento de casos de sífilis en las Américas (22-05-2024).</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://www.paho.org/es/noticias/22-5-2024-casos-sifilis-aumentan-americas</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>S21</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>OMS, nuevo informe: aumento importante de ITS (21-05-2024).</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://www.who.int/news/item/21-05-2024-new-report-flags-major-increase-in-sexually-transmitted-infections---amidst-challenges-in-hiv-and-hepatitis</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>S22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>MINSAL, Norma de Profilaxis, Diagnóstico y Tratamiento de las ITS (NT 187, 2016).</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://diprece.minsal.cl/wrdprss_minsal/wp-content/uploads/2014/11/NORMA-GRAL.-TECNICA-N°-187-DE-PROFILAXIS-DIAGNOSTICO-Y-TRATAMIENTO-DE-LAS-ITS.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>S23</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>MINSAL, convenio con el Colegio de Matronas para prevención de VIH/ITS (2019).</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://www.minsal.cl/?p=51074</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>S24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Protocolo de test rápido de VIH en Chile (vía Pauta).</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://www.pauta.cl/cronica/como-funciona-el-protocolo-del-test-rapido-del-vih-chile</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>S25</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>MINSAL, Norma Técnica Hepatitis B y C (2025).</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://diprece.minsal.cl/wp-content/uploads/2025/12/2025.12.05_NORMA-TECNICA-HEPATITIS-B-Y-C.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>S26</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ChileAtiende, vacuna contra el VPH.</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://chileatiende.gob.cl/fichas/36896-vacuna-contra-el-virus-del-papiloma-humano-vph</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>S27</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>OMS, notas descriptivas: sífilis, gonorrea, clamidia, tricomoniasis, herpes, VPH, hepatitis B, vaginosis bacteriana.</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://www.who.int/news-room/fact-sheets</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>S28</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>CDC, guías de tratamiento de ITS 2021.</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://www.cdc.gov/std/treatment-guidelines/</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>S29</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Sífilis congénita 2021 y 2025 (vía La Ventana Ciudadana).</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://laventanaciudadana.cl/vigilancia-epidemiologica-el-radar-de-la-salud-publica-frente-a-la-sifilis-en-chile/</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>S30</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Gonorrea en Chile 2010–2017 (vía El Desconcierto, 2018).</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://eldesconcierto.cl/2018/09/11/contagio-de-gonorrea-se-duplico-en-chile-durante-los-ultimos-siete-anos</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>S35</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ISP: Boletín Resultados confirmación de infección por VIH, Chile 2010–2022 (informe oficial).</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://www.ispch.gob.cl/boletin/resultados-confirmacion-de-infeccion-por-vih-chile-2010-2022/</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>S36</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Rev Chil Infectol 2024: Situación epidemiológica de VIH a nivel global y nacional, puesta al día.</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://www.scielo.cl/scielo.php?script=sci_arttext&amp;pid=S0716-10182024000200248</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>S37</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>MINSAL, Departamento de Epidemiología: Situación epidemiológica de sífilis en Chile 2016 (Rev Chil Infectol 2018).</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://www.scielo.cl/article_plus.php?pid=S0716-10182018000300284&amp;tlng=es&amp;lng=es</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>S38</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Rev Chil Obstet Ginecol: Vigilancia epidemiológica de sífilis en Chile.</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://www.scielo.cl/pdf/rchog/v78n5/art11.pdf</t>
-        </is>
+      <c r="A12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Opcion</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Orden</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Sí, desde los 14 años</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>No (como hoy en los colegios)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5008,6 +6877,1171 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>S29</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Escenario</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Porcentaje</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Orden</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Alto (10%)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Conservador (5%)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Puntos</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Orden</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Orden</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Nacimientos 15–19</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>4979</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Embarazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Gonorrea</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2682</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>ITS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Sífilis</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>11155</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>ITS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Orden</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Supuesto</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>PorQue</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>FuenteID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Colegios con matrona y educación sexual integral</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lo eliges tú (0% a 100%)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Qué parte de los colegios tendría una matrona haciendo educación sexual integral</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Supuesto del escenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Entrega de anticonceptivos desde los 14 años</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Sí o No</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>La Ley 20.418 garantiza información y acceso a métodos; desde los 14 años la consulta es confidencial</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>S40</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Efecto en los embarazos adolescentes con educación + acceso</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>5% (conservador) o 10% (alto)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>El acceso gratuito a DIU e implantes redujo los nacimientos adolescentes entre 5% y 10% en 4 años</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>S41</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Efecto de la educación sola, sin acceso a métodos</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Los programas escolares sin acceso a anticonceptivos no mostraron un efecto claro en embarazos</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>S42</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Aumento del uso de condón gracias a la educación</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Lo eliges tú (0 a 20 puntos)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>La educación sexual integral aumenta el uso de condón y anticonceptivos (OMS)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>S43</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Protección del condón</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>El uso consistente del condón reduce cerca de 80% la transmisión del VIH; se usa como supuesto para las demás ITS</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>S42N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Datos base</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>4.979 nacimientos de madres de 15 a 19 (2025) · tasa 8,3 por 1.000 · 2.682 casos de gonorrea y 11.155 de sífilis (2025)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Cifras oficiales del último año disponible</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>FuenteID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Referencia</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rev Chil Infectol 2025. Caracterización epidemiológica de la sífilis en Chile 2018–2022 (datos de notificación MINSAL).</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://revinf.cl/index.php/revinf/article/download/2492/1138</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MINSAL, Informe Epidemiológico Anual 2025 de sífilis (vía Meganoticias, 19-08-2026).</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.meganoticias.cl/nacional/529712-sifilis-alcanza-record-historico-en-chile-casos-se-disparan-aumento-entre-adultos-mayores-y-mujeres-60-anos-19-08-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MINSAL, reporte 2025 de sífilis y gonorrea (vía Emol, 12-07-2026).</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.emol.com/noticias/Nacional/2026/07/12/1205310/sifilis-gonorrea-chile-reporte-minsal.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MINSAL, gonorrea y sífilis en jóvenes 2025 (vía BioBioChile, 06-07-2026).</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.biobiochile.cl/noticias/salud-y-bienestar/cuerpo/2026/07/06/registro-mas-alto-de-la-decada-aumentan-los-contagios-de-gonorrea-y-sifilis-entre-jovenes-chilenos.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MINSAL, sífilis en personas de 60 años o más (vía BioBioChile, 19-08-2026).</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.biobiochile.cl/noticias/nacional/chile/2026/08/19/sifilis-alcanza-record-en-chile-tasa-entre-mujeres-mayores-de-60-anos-se-duplico-en-cuatro-anos.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MINSAL, ITS en menores de 15 años (vía T13, 19-08-2026).</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.t13.cl/noticia/nacional/aumento-ets-chile-destaca-incremento-gonorrea-menores-15-anos-sifilis-record-19-8-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ISP, confirmación de VIH 2010–2019 (documento Cámara de Diputados).</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.camara.cl/verDoc.aspx?prmID=172229&amp;prmTIPO=DOCUMENTOCOMISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ISP, VIH 2022 (vía BioBioChile, 31-07-2023).</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.biobiochile.cl/noticias/nacional/chile/2023/07/31/isp-casos-de-vih-aumenta-7-en-un-ano-y-mayor-tasa-de-diagnostico-esta-asociada-a-hombres.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ISP, VIH 2024 (vía El Ciudadano).</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.elciudadano.com/?p=1117920</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ISP, VIH 2025 (vía El Desconcierto, 23-03-2026).</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://eldesconcierto.cl/2026/03/23/vih-una-inercia-preocupante</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VIH 2023 por sexo y edad (vía El Mostrador, 01-12-2025).</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.elmostrador.cl/agenda-pais/vida-en-linea/2025/12/01/vih-en-chile-expertos-alertan-fuerte-aumento-de-casos-en-jovenes-y-baja-percepcion-de-riesgo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ONUSIDA, personas que viven con VIH en Chile (vía The Clinic, 25-06-2026).</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.theclinic.cl/2026/06/25/chile-registra-un-aumento-de-casos-de-vih-de-un-86-en-los-ultimos-10-anos-onu-alerta-sobre-riesgos-de-no-avanzar-en-prevencion-de-contagios/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cascada VIH Chile: diagnosticados sin tratamiento (vía BioBioChile, 03-09-2026).</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.biobiochile.cl/noticias/nacional/chile/2026/09/03/alerta-por-vih-en-chile-mas-de-21-mil-diagnosticados-no-reciben-tratamiento.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ONUSIDA, informe Latinoamérica 2025.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://unaids.org.br/wp-content/uploads/2025/07/25-07-09-BLS25218-GR-RP-LATAM-PTBR-2.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ONUSIDA, ficha mundial.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.unaids.org/en/resources/fact-sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ECDC, sífilis, informe anual 2024.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/publications-data/syphilis-annual-epidemiological-report-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ECDC, gonorrea, informe anual 2024.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/publications-data/gonorrhoea-annual-epidemiological-report-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ECDC, vigilancia de VIH/sida en Europa 2025 (datos 2024).</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/publications-data/hivaids-surveillance-europe-2025-2024-data</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>OPS, perfil de país Chile.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://hia.paho.org/en/country-profiles/chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>OPS, aumento de casos de sífilis en las Américas (22-05-2024).</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.paho.org/es/noticias/22-5-2024-casos-sifilis-aumentan-americas</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>OMS, nuevo informe: aumento importante de ITS (21-05-2024).</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news/item/21-05-2024-new-report-flags-major-increase-in-sexually-transmitted-infections---amidst-challenges-in-hiv-and-hepatitis</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MINSAL, Norma de Profilaxis, Diagnóstico y Tratamiento de las ITS (NT 187, 2016).</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://diprece.minsal.cl/wrdprss_minsal/wp-content/uploads/2014/11/NORMA-GRAL.-TECNICA-N°-187-DE-PROFILAXIS-DIAGNOSTICO-Y-TRATAMIENTO-DE-LAS-ITS.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>S23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MINSAL, convenio con el Colegio de Matronas para prevención de VIH/ITS (2019).</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.minsal.cl/?p=51074</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>S24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Protocolo de test rápido de VIH en Chile (vía Pauta).</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.pauta.cl/cronica/como-funciona-el-protocolo-del-test-rapido-del-vih-chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MINSAL, Norma Técnica Hepatitis B y C (2025).</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://diprece.minsal.cl/wp-content/uploads/2025/12/2025.12.05_NORMA-TECNICA-HEPATITIS-B-Y-C.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ChileAtiende, vacuna contra el VPH.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://chileatiende.gob.cl/fichas/36896-vacuna-contra-el-virus-del-papiloma-humano-vph</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>S27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>OMS, notas descriptivas: sífilis, gonorrea, clamidia, tricomoniasis, herpes, VPH, hepatitis B, vaginosis bacteriana.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news-room/fact-sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CDC, guías de tratamiento de ITS 2021.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/std/treatment-guidelines/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sífilis congénita 2021 y 2025 (vía La Ventana Ciudadana).</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://laventanaciudadana.cl/vigilancia-epidemiologica-el-radar-de-la-salud-publica-frente-a-la-sifilis-en-chile/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>S30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Gonorrea en Chile 2010–2017 (vía El Desconcierto, 2018).</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://eldesconcierto.cl/2018/09/11/contagio-de-gonorrea-se-duplico-en-chile-durante-los-ultimos-siete-anos</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>S35</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ISP: Boletín Resultados confirmación de infección por VIH, Chile 2010–2022 (informe oficial).</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.ispch.gob.cl/boletin/resultados-confirmacion-de-infeccion-por-vih-chile-2010-2022/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>S36</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Rev Chil Infectol 2024: Situación epidemiológica de VIH a nivel global y nacional, puesta al día.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.scielo.cl/scielo.php?script=sci_arttext&amp;pid=S0716-10182024000200248</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>S37</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MINSAL, Departamento de Epidemiología: Situación epidemiológica de sífilis en Chile 2016 (Rev Chil Infectol 2018).</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.scielo.cl/article_plus.php?pid=S0716-10182018000300284&amp;tlng=es&amp;lng=es</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>S38</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Rev Chil Obstet Ginecol: Vigilancia epidemiológica de sífilis en Chile.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.scielo.cl/pdf/rchog/v78n5/art11.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>S39</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Weller S, Davis K. Condom effectiveness in reducing heterosexual HIV transmission. Cochrane Database Syst Rev 2002 (reducción cercana a 80%).</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/14651858.CD003255</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>S40</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ley 20.418 (2010): normas sobre información, orientación y prestaciones en materia de regulación de la fertilidad.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.bcn.cl/leychile/navegar?idNorma=1010482</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>S41</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Lindo y Packham (UC Davis): acceso a anticonceptivos de larga duración y nacimientos adolescentes.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.nber.org/papers/w21544</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>S42</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Mason-Jones et al., Cochrane 2016: educación sexual escolar para prevenir ITS y embarazo.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/14651858.CD006417.pub3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>S43</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>OMS, nota descriptiva: educación sexual integral.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news-room/questions-and-answers/item/comprehensive-sexuality-education</t>
         </is>
       </c>
     </row>
@@ -5096,7 +8130,6 @@
       <c r="E2" t="n">
         <v>36.6</v>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>S3</t>
@@ -5125,7 +8158,6 @@
       <c r="E3" t="n">
         <v>44.8</v>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>S3</t>
@@ -5253,7 +8285,6 @@
       <c r="E7" t="n">
         <v>103.5</v>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>S3</t>
@@ -5348,7 +8379,6 @@
       <c r="E10" t="n">
         <v>44.9</v>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>S11</t>
@@ -5377,7 +8407,6 @@
       <c r="E11" t="n">
         <v>59.2</v>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>S11</t>
@@ -5439,7 +8468,6 @@
       <c r="E13" t="n">
         <v>46.1</v>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>S11</t>

--- a/dashboard-its-chile/ITS_Chile_BaseDatos.xlsx
+++ b/dashboard-its-chile/ITS_Chile_BaseDatos.xlsx
@@ -30,7 +30,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SimCondon" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SimIndicadores" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SimSupuestos" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TodasITS" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChileMundoITS" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -367,7 +369,39 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="Fuentes" displayName="Fuentes" ref="A1:C40" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="TodasITS" displayName="TodasITS" ref="A1:G11" headerRowCount="1">
+  <autoFilter ref="A1:G11"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Orden"/>
+    <tableColumn id="2" name="ITS"/>
+    <tableColumn id="3" name="Chile"/>
+    <tableColumn id="4" name="Vigilancia"/>
+    <tableColumn id="5" name="Mundo"/>
+    <tableColumn id="6" name="QueEs"/>
+    <tableColumn id="7" name="FuenteID"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="ChileMundoITS" displayName="ChileMundoITS" ref="A1:G10" headerRowCount="1">
+  <autoFilter ref="A1:G10"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="ITS"/>
+    <tableColumn id="2" name="OrdenITS"/>
+    <tableColumn id="3" name="Lugar"/>
+    <tableColumn id="4" name="OrdenLugar"/>
+    <tableColumn id="5" name="Tasa"/>
+    <tableColumn id="6" name="Anio"/>
+    <tableColumn id="7" name="FuenteID"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="Fuentes" displayName="Fuentes" ref="A1:C54" headerRowCount="1">
   <autoFilter ref="A1:C35"/>
   <tableColumns count="3">
     <tableColumn id="1" name="FuenteID"/>
@@ -785,7 +819,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -7357,7 +7390,762 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Orden</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>ITS</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Vigilancia</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Mundo</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>QueEs</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>FuenteID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Sífilis</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>11.155 casos · 55,2 por 100 mil (2025)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Notificación obligatoria</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>8 millones de casos nuevos al año (2022)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Bacteria · se cura con penicilina</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>S2;S21;S47</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Gonorrea</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2.682 casos · 13,3 por 100 mil (2025)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Notificación obligatoria</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>82 millones de casos nuevos al año (2020)</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Bacteria · se cura con antibiótico</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>S4;S27;S47</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>VIH</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>4.313 diagnósticos (2025) · 91.000 viven con VIH</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Notificación obligatoria</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>41 millones viven con VIH; 1,2 millones de infecciones nuevas (2025)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Virus · tratamiento de por vida; indetectable = intransmisible</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>S10;S12;S46;S47</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>609 casos (2021) · 2 de cada 3 por vía sexual</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Notificación obligatoria</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>254 millones viven con hepatitis B (2022)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Virus · se previene con vacuna</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>S25;S54;S47</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>1.455 confirmados (jun 2022 – jun 2024)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Solo laboratorio o estudios</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Más de 180 mil casos y 492 muertes (2022 – mar 2026)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Virus · notificación inmediata como evento emergente</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>S56;S55</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Clamidia</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Sin tasa nacional · 5,9% en embarazadas de Santiago (estudio 2010–11)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Solo laboratorio o estudios</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>129 millones de casos nuevos al año (2020)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Bacteria · se cura con antibiótico; suele no dar síntomas</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>S48;S49;S47</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>VPH (virus papiloma)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>17,1% en mujeres en tamizaje (estudio 2014–2023)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Solo laboratorio o estudios</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>1 de cada 3 hombres tiene VPH genital</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Virus · se previene con vacuna; causa cáncer cervicouterino</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>S50;S51</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Herpes genital</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Sin dato poblacional</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>No se vigila</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>520 millones viven con herpes tipo 2</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Virus · no se cura; los brotes se tratan</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>S52</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Tricomoniasis</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>2,4% en embarazadas de Santiago (estudio 2010–11)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>No se vigila</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>156 millones de casos nuevos al año (2020)</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Parásito · se cura con antibiótico</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>S48;S53</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Linfogranuloma venéreo</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Sin dato público</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>No se vigila</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Europa: 3.490 casos (2024)</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Bacteria (clamidia L1–L3) · se cura con antibiótico</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>S57</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ITS</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>OrdenITS</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Lugar</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>OrdenLugar</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Tasa</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Anio</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>FuenteID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Sífilis</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sífilis</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>S44</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sífilis</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Unión Europea</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>VIH (diagnósticos)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>2025 (cálculo propio)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>VIH (diagnósticos)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>S45</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>VIH (diagnósticos)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Unión Europea</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>S18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Gonorrea</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Gonorrea</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>S44</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Gonorrea</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Unión Europea</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8042,6 +8830,244 @@
       <c r="C40" t="inlineStr">
         <is>
           <t>https://www.who.int/news-room/questions-and-answers/item/comprehensive-sexuality-education</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>S44</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CDC, Sexually Transmitted Infections Surveillance 2023 (tasas de sífilis, gonorrea y clamidia en EE.UU.).</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/sti-statistics/annual/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>S45</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CDC, HIV Surveillance Report: diagnósticos de VIH 2023 en EE.UU.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://stacks.cdc.gov/view/cdc/177771</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>S46</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ONUSIDA, ficha mundial 2026 (datos 2025).</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.unaids.org/sites/default/files/2026-06/20260612_Global_HIV_Factsheet.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>S47</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Decreto 7/2019 MINSAL: reglamento de enfermedades de notificación obligatoria.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.diariooficial.interior.gob.cl/publicaciones/2020/01/24/42561/01/1715587.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>S48</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Rev Chil Infectol 2012: Chlamydia trachomatis y Trichomonas vaginalis en embarazadas de Santiago.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://pesquisa.bvsalud.org/gim/resource/en/lil-660024</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>S49</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>OMS, nota descriptiva: clamidia.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news-room/fact-sheets/detail/chlamydia</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>S50</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Rev Méd Chile 2026: prevalencia de VPH en mujeres en tamizaje (Huechuraba 2014–2023).</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.revistamedicadechile.cl/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>S51</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>OMS 2023: uno de cada tres hombres en el mundo tiene VPH genital.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news/item/01-09-2023-one-in-three-men-worldwide-are-infected-with-genital-human-papillomavirus</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>S52</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>OMS 2024: más de 1 de cada 5 adultos en el mundo tiene herpes genital.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news/item/11-12-2024-over-1-in-5-adults-worldwide-has-a-genital-herpes-infection-who</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>S53</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>OMS, nota descriptiva: tricomoniasis.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news-room/fact-sheets/detail/Trichomoniasis</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>S54</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>OPS/OMS 2024: hepatitis virales en el mundo (Informe mundial de hepatitis 2024).</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.paho.org/en/news/10-4-2024-who-sounds-alarm-viral-hepatitis-infections-claiming-3500-lives-each-day</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>S55</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>OPS, actualización epidemiológica de mpox (abril 2026).</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.paho.org/sites/default/files/2026/04/23042026actualizacion-epi-mpoxesfinal.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>S56</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MINSAL, casos de mpox en Chile 2022–2024 (vía El Dínamo, 14-08-2024).</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.eldinamo.cl/sociedad/2024/08/14/oms-declara-emergencia-sanitaria-internacional-por-viruela-del-mono-cuantos-casos-hay-en-chile-y-como-se-contagia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>S57</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ECDC, linfogranuloma venéreo, informe anual 2024.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/publications-data/lymphogranuloma-venereum-annual-epidemiological-report-2024</t>
         </is>
       </c>
     </row>
